--- a/templates/session_template.xlsx
+++ b/templates/session_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alisk\OneDrive\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alisk\NAKOL_tests\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BC9701-172D-44BB-B5A4-4DD892DD9BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F846C626-135B-434A-96BA-D2CB94DF1ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Дата(формат XX.XX.XX)</t>
   </si>
@@ -33,10 +33,13 @@
     <t>Предмет</t>
   </si>
   <si>
-    <t>Время (Формат: XX:XX)</t>
-  </si>
-  <si>
     <t>Аудитория</t>
+  </si>
+  <si>
+    <t>Время начала(Формат: XX:XX)</t>
+  </si>
+  <si>
+    <t>Время окончания(Формат: ХХ:ХХ)</t>
   </si>
 </sst>
 </file>
@@ -354,27 +357,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.21875" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" customWidth="1"/>
     <col min="4" max="4" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
